--- a/output/graficos_regionales/plot_i_peringrmin_a_2018_araucania.xlsx
+++ b/output/graficos_regionales/plot_i_peringrmin_a_2018_araucania.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,11 +385,6 @@
           <t>valor_previo</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>seleccionado</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -408,9 +403,6 @@
       <c r="D2">
         <v>2.77</v>
       </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -429,9 +421,6 @@
       <c r="D3">
         <v>3.54</v>
       </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -450,9 +439,6 @@
       <c r="D4">
         <v>3.6</v>
       </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="D5">
         <v>3.94</v>
       </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -492,9 +475,6 @@
       <c r="D6">
         <v>4.27</v>
       </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -513,9 +493,6 @@
       <c r="D7">
         <v>5.4</v>
       </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -534,9 +511,6 @@
       <c r="D8">
         <v>5.59</v>
       </c>
-      <c r="G8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -555,9 +529,6 @@
       <c r="D9">
         <v>5.67</v>
       </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -576,9 +547,6 @@
       <c r="D10">
         <v>5.96</v>
       </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -597,9 +565,6 @@
       <c r="D11">
         <v>6.53</v>
       </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -618,9 +583,6 @@
       <c r="D12">
         <v>6.54</v>
       </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -639,9 +601,6 @@
       <c r="D13">
         <v>7.3</v>
       </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -660,9 +619,6 @@
       <c r="D14">
         <v>7.66</v>
       </c>
-      <c r="G14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -681,9 +637,6 @@
       <c r="D15">
         <v>7.98</v>
       </c>
-      <c r="G15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -702,9 +655,6 @@
       <c r="D16">
         <v>8.390000000000001</v>
       </c>
-      <c r="G16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -722,9 +672,6 @@
       </c>
       <c r="D17">
         <v>8.69</v>
-      </c>
-      <c r="G17" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
